--- a/data/processed/harmonization/Nitrogen__Dissolved_organic_nitrogen/harmonized.xlsx
+++ b/data/processed/harmonization/Nitrogen__Dissolved_organic_nitrogen/harmonized.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>East_River:1</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2016-09-12:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>East_River:2</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2016-09-12:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>East_River:3</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2016-09-12:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>East_River:4</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2016-09-12:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>East_River:5</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2016-09-12:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>East_River:6</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2016-09-12:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>East_River:7</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2016-09-12:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>East_River:8</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2016-09-12:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>East_River:9</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2016-09-12:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>East_River:10</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2016-09-12:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>East_River:11</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2016-09-12:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>East_River:12</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2016-09-12:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>East_River:13</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2016-09-12:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>East_River:14</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2016-09-12:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>East_River:15</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2016-09-12:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>East_River:16</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2016-09-12:16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>East_River:17</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2016-09-12:17</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>East_River:18</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2016-09-12:18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>East_River:19</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2016-09-12:19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>East_River:20</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2016-09-12:20</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>East_River:21</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2016-09-12:21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>East_River:22</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2016-09-12:22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>East_River:23</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2016-09-12:23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>East_River:24</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2016-09-12:24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>East_River:25</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2016-09-12:25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>East_River:26</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2016-09-12:26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>East_River:27</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2016-09-12:27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>East_River:28</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2016-09-12:28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>East_River:29</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2016-09-12:29</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>East_River:30</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2016-09-12:30</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>East_River:31</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2016-09-12:31</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>East_River:32</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2016-09-12:32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>East_River:33</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2016-09-12:33</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>East_River:34</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2016-09-12:34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>East_River:35</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2016-09-12:35</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>East_River:36</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2016-09-12:36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>East_River:37</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Upslope:1:0-5:2016-09-12:37</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>East_River:38</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Upslope:1:5-15:2016-09-12:38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>East_River:39</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Upslope:1:15 cm +:2016-09-12:39</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>East_River:40</t>
+          <t>F2:East_River:Pumphouse_Floodplain:Upslope:2:0-5:2016-09-12:40</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>East_River:41</t>
+          <t>F2:East_River:Pumphouse_Floodplain:Upslope:2:5-15:2016-09-12:41</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>East_River:42</t>
+          <t>F2:East_River:Pumphouse_Floodplain:Upslope:2:15 cm +:2016-09-12:42</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>East_River:43</t>
+          <t>F3:East_River:Pumphouse_Floodplain:Upslope:3:0-5:2016-09-12:43</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>East_River:44</t>
+          <t>F3:East_River:Pumphouse_Floodplain:Upslope:3:5-15:2016-09-12:44</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>East_River:45</t>
+          <t>F3:East_River:Pumphouse_Floodplain:Upslope:3:15 cm +:2016-09-12:45</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:67</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2016-10-20:67</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:68</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2016-10-20:68</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:69</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2016-10-20:69</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:70</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:1:0-5:2016-10-20:70</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:71</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:1:5-15:2016-10-20:71</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:72</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:1:15 cm +:2016-10-20:72</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:73</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2016-10-20:73</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:74</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2016-10-20:74</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:75</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2016-10-20:75</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:76</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:1:0-5:2016-10-20:76</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:77</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:1:5-15:2016-10-20:77</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:78</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:1:15 cm +:2016-10-20:78</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:79</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2016-10-20:79</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:80</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2016-10-20:80</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:81</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2016-10-20:81</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:82</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:1:0-5:2016-10-20:82</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:83</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:1:5-15:2016-10-20:83</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:84</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:1:15 cm +:2016-10-20:84</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:85</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Upslope:1:0-5:2016-10-20:85</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:86</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Upslope:1:5-15:2016-10-20:86</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:87</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Upslope:1:15 cm +:2016-10-20:87</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:88</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Downslope:1:0-5:2016-10-20:88</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:89</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Downslope:1:5-15:2016-10-20:89</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:90</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Downslope:1:15 cm +:2016-10-20:90</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:91</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Upslope:1:0-5:2016-10-20:91</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:92</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Upslope:1:5-15:2016-10-20:92</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:93</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Upslope:1:15 cm +:2016-10-20:93</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:94</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Downslope:1:0-5:2016-10-20:94</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:95</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Downslope:1:5-15:2016-10-20:95</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:96</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Downslope:1:15 cm +:2016-10-20:96</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:97</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Upslope:1:0-5:2016-10-20:97</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:98</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Upslope:1:5-15:2016-10-20:98</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:99</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Upslope:1:15 cm +:2016-10-20:99</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:100</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Downslope:1:0-5:2016-10-20:100</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:101</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Downslope:1:5-15:2016-10-20:101</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:102</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Downslope:1:15 cm +:2016-10-20:102</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:103</t>
+          <t>A1:Washington_Gulch:Alpine:Upslope:1:0-5:2016-10-20:103</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:104</t>
+          <t>A1:Washington_Gulch:Alpine:Upslope:1:5-15:2016-10-20:104</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:105</t>
+          <t>A1:Washington_Gulch:Alpine:Upslope:1:15 cm +:2016-10-20:105</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:107</t>
+          <t>A1:Washington_Gulch:Alpine:Downslope:1:5-15:2016-10-20:107</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>East_River:112</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:1:0-5:2017-03-07:112</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>East_River:113</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:1:5-15:2017-03-07:113</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>East_River:114</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:1:15 cm +:2017-03-07:114</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>East_River:115</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:2:0-5:2017-03-07:115</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>East_River:116</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:2:5-15:2017-03-07:116</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>East_River:117</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:2:15 cm +:2017-03-07:117</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5262,12 +5262,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>East_River:119</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:1:5-15:2017-03-07:119</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>East_River:120</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:1:15 cm +:2017-03-07:120</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>East_River:121</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:2:0-5:2017-03-07:121</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>East_River:122</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:2:5-15:2017-03-07:122</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>East_River:124</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:1:0-5:2017-03-07:124</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>East_River:125</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:1:5-15:2017-03-07:125</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>East_River:126</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:1:15 cm +:2017-03-07:126</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>East_River:127</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:2:0-5:2017-03-07:127</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>East_River:128</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:2:5-15:2017-03-07:128</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>East_River:133</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:1:0-5:2017-05-09:133</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>East_River:134</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:2:5-15:2017-05-09:134</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>East_River:137</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:2:5-15:2017-05-09:137</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>East_River:138</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:3:15 cm +:2017-05-09:138</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>East_River:140</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:2:5-15:2017-05-09:140</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>East_River:141</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:3:15 cm +:2017-05-09:141</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>East_River:142</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:1:0-5:2017-05-09:142</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>East_River:143</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:2:5-15:2017-05-09:143</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>East_River:144</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:3:15 cm +:2017-05-09:144</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>East_River:145</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:1:0-5:2017-05-09:145</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>East_River:146</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:2:5-15:2017-05-09:146</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>East_River:147</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:3:15 cm +:2017-05-09:147</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>East_River:148</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:1:0-5:2017-05-09:148</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>East_River:149</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:2:5-15:2017-05-09:149</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>East_River:150</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:3:15 cm +:2017-05-09:150</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>East_River:151</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:1:0-5:2017-05-09:151</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6630,12 +6630,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>East_River:152</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:2:5-15:2017-05-09:152</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>East_River:154</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:1:0-5:2017-05-09:154</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>East_River:155</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:2:5-15:2017-05-09:155</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>East_River:156</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:3:15 cm +:2017-05-09:156</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>East_River:157</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:1:0-5:2017-05-09:157</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>East_River:158</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:2:5-15:2017-05-09:158</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>East_River:159</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:3:15 cm +:2017-05-09:159</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>East_River:160</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-05-09:160</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>East_River:161</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-05-09:161</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>East_River:162</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-05-09:162</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>East_River:163</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-05-09:163</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>East_River:164</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-05-09:164</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>East_River:165</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-05-09:165</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>East_River:166</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-05-09:166</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>East_River:167</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-05-09:167</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>East_River:168</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-05-09:168</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>East_River:172</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-06-09:172</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>East_River:173</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2017-06-09:173</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>East_River:174</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-06-09:174</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>East_River:175</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2017-06-09:175</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>East_River:176</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2017-06-09:176</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>East_River:177</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2017-06-09:177</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>East_River:178</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2017-06-09:178</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>East_River:179</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2017-06-09:179</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>East_River:180</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2017-06-09:180</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>East_River:181</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-06-09:181</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -8002,12 +8002,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>East_River:182</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2017-06-09:182</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>East_River:183</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-06-09:183</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>East_River:184</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-06-09:184</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>East_River:185</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2017-06-09:185</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>East_River:188</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2017-06-09:188</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>East_River:190</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2017-06-09:190</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>East_River:191</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2017-06-09:191</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>East_River:192</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2017-06-09:192</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
